--- a/InputData/bldgs/EoDSDwSP/Elasticity of Dist Solar Deployment wrt Subsidy Perc.xlsx
+++ b/InputData/bldgs/EoDSDwSP/Elasticity of Dist Solar Deployment wrt Subsidy Perc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\bldgs\EoDSDwSP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\EoDSDwSP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7E60EC-3329-461B-BAA2-DC75E0655131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FB24AB-1255-468C-977F-D5601018184B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26430" yWindow="1485" windowWidth="26400" windowHeight="14490" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>Source:</t>
   </si>
@@ -98,6 +98,15 @@
   </si>
   <si>
     <t>Elasticity (dimensionless)</t>
+  </si>
+  <si>
+    <t>Data Centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. They copy the commercial value so the elasticity is defined; it has no effect because data centers have no distributed solar potential.</t>
   </si>
 </sst>
 </file>
@@ -152,7 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -164,6 +173,9 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -518,6 +530,14 @@
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="360" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +648,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
@@ -666,6 +686,15 @@
         <v>1.2661498708010337</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="6">
+        <f>B4</f>
+        <v>1.2661498708010337</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
